--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560143</v>
+        <v>128561756</v>
       </c>
       <c r="B2" t="n">
         <v>79083</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490382</v>
+        <v>490192</v>
       </c>
       <c r="R2" t="n">
-        <v>6726363</v>
+        <v>6726244</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128561756</v>
+        <v>128560143</v>
       </c>
       <c r="B3" t="n">
         <v>79083</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490192</v>
+        <v>490382</v>
       </c>
       <c r="R3" t="n">
-        <v>6726244</v>
+        <v>6726363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128561671</v>
+        <v>128562050</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R14" t="n">
-        <v>6726241</v>
+        <v>6726251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562050</v>
+        <v>128561671</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2116,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R15" t="n">
-        <v>6726251</v>
+        <v>6726241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,12 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128561756</v>
+        <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490192</v>
+        <v>490382</v>
       </c>
       <c r="R2" t="n">
-        <v>6726244</v>
+        <v>6726363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128560143</v>
+        <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490382</v>
+        <v>490192</v>
       </c>
       <c r="R3" t="n">
-        <v>6726363</v>
+        <v>6726244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128560176</v>
+        <v>128561306</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490378</v>
+        <v>490251</v>
       </c>
       <c r="R6" t="n">
-        <v>6726345</v>
+        <v>6726207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128561306</v>
+        <v>128561769</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490251</v>
+        <v>490197</v>
       </c>
       <c r="R7" t="n">
-        <v>6726207</v>
+        <v>6726291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128561769</v>
+        <v>128560176</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490197</v>
+        <v>490378</v>
       </c>
       <c r="R8" t="n">
-        <v>6726291</v>
+        <v>6726345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128562050</v>
+        <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R14" t="n">
-        <v>6726251</v>
+        <v>6726241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128561671</v>
+        <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R15" t="n">
-        <v>6726241</v>
+        <v>6726251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2161,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128560322</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>128560363</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>128561664</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128560121</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128560783</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128561769</v>
+        <v>128560176</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1251,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490197</v>
+        <v>490378</v>
       </c>
       <c r="R7" t="n">
-        <v>6726291</v>
+        <v>6726345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128560176</v>
+        <v>128561769</v>
       </c>
       <c r="B8" t="n">
         <v>79087</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490378</v>
+        <v>490197</v>
       </c>
       <c r="R8" t="n">
-        <v>6726345</v>
+        <v>6726291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560602</v>
+        <v>128560947</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490357</v>
+        <v>490328</v>
       </c>
       <c r="R21" t="n">
-        <v>6726365</v>
+        <v>6726400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2813,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560322</v>
+        <v>128560602</v>
       </c>
       <c r="B22" t="n">
         <v>79087</v>
@@ -2870,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490359</v>
+        <v>490357</v>
       </c>
       <c r="R22" t="n">
-        <v>6726325</v>
+        <v>6726365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560164</v>
+        <v>128560322</v>
       </c>
       <c r="B23" t="n">
         <v>79087</v>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490378</v>
+        <v>490359</v>
       </c>
       <c r="R23" t="n">
-        <v>6726352</v>
+        <v>6726325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560363</v>
+        <v>128560164</v>
       </c>
       <c r="B24" t="n">
         <v>79087</v>
@@ -3084,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490366</v>
+        <v>490378</v>
       </c>
       <c r="R24" t="n">
-        <v>6726348</v>
+        <v>6726352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560947</v>
+        <v>128560363</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490328</v>
+        <v>490366</v>
       </c>
       <c r="R25" t="n">
-        <v>6726400</v>
+        <v>6726348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,12 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128561306</v>
+        <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490251</v>
+        <v>490378</v>
       </c>
       <c r="R6" t="n">
-        <v>6726207</v>
+        <v>6726345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128560176</v>
+        <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490378</v>
+        <v>490251</v>
       </c>
       <c r="R7" t="n">
-        <v>6726345</v>
+        <v>6726207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128560102</v>
+        <v>128561932</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490383</v>
+        <v>490206</v>
       </c>
       <c r="R11" t="n">
-        <v>6726365</v>
+        <v>6726252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128561932</v>
+        <v>128561685</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490206</v>
+        <v>490192</v>
       </c>
       <c r="R12" t="n">
-        <v>6726252</v>
+        <v>6726243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128561685</v>
+        <v>128560102</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490192</v>
+        <v>490383</v>
       </c>
       <c r="R13" t="n">
-        <v>6726243</v>
+        <v>6726365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
         <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560947</v>
+        <v>128560164</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,39 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490328</v>
+        <v>490378</v>
       </c>
       <c r="R21" t="n">
-        <v>6726400</v>
+        <v>6726352</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2813,12 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560602</v>
+        <v>128560363</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490357</v>
+        <v>490366</v>
       </c>
       <c r="R22" t="n">
-        <v>6726365</v>
+        <v>6726348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560322</v>
+        <v>128560947</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2953,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490359</v>
+        <v>490328</v>
       </c>
       <c r="R23" t="n">
-        <v>6726325</v>
+        <v>6726400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3027,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560164</v>
+        <v>128560602</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490378</v>
+        <v>490357</v>
       </c>
       <c r="R24" t="n">
-        <v>6726352</v>
+        <v>6726365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560363</v>
+        <v>128560322</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490366</v>
+        <v>490359</v>
       </c>
       <c r="R25" t="n">
-        <v>6726348</v>
+        <v>6726325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128561932</v>
+        <v>128560102</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490206</v>
+        <v>490383</v>
       </c>
       <c r="R11" t="n">
-        <v>6726252</v>
+        <v>6726365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128561685</v>
+        <v>128561932</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490192</v>
+        <v>490206</v>
       </c>
       <c r="R12" t="n">
-        <v>6726243</v>
+        <v>6726252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128560102</v>
+        <v>128561685</v>
       </c>
       <c r="B13" t="n">
         <v>79089</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490383</v>
+        <v>490192</v>
       </c>
       <c r="R13" t="n">
-        <v>6726365</v>
+        <v>6726243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562050</v>
+        <v>128562020</v>
       </c>
       <c r="B15" t="n">
         <v>79089</v>
@@ -2119,7 +2119,7 @@
         <v>490205</v>
       </c>
       <c r="R15" t="n">
-        <v>6726251</v>
+        <v>6726253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,11 +2162,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562020</v>
+        <v>128562050</v>
       </c>
       <c r="B16" t="n">
         <v>79089</v>
@@ -2231,7 +2226,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726253</v>
+        <v>6726251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2269,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2728,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560164</v>
+        <v>128560602</v>
       </c>
       <c r="B21" t="n">
         <v>79089</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490378</v>
+        <v>490357</v>
       </c>
       <c r="R21" t="n">
-        <v>6726352</v>
+        <v>6726365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2835,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560363</v>
+        <v>128560322</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490366</v>
+        <v>490359</v>
       </c>
       <c r="R22" t="n">
-        <v>6726348</v>
+        <v>6726325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560947</v>
+        <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,39 +2953,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490328</v>
+        <v>490378</v>
       </c>
       <c r="R23" t="n">
-        <v>6726400</v>
+        <v>6726352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,12 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3049,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560602</v>
+        <v>128560363</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -3094,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490357</v>
+        <v>490366</v>
       </c>
       <c r="R24" t="n">
-        <v>6726365</v>
+        <v>6726348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560322</v>
+        <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,34 +3167,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490359</v>
+        <v>490328</v>
       </c>
       <c r="R25" t="n">
-        <v>6726325</v>
+        <v>6726400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3241,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560143</v>
+        <v>128561756</v>
       </c>
       <c r="B2" t="n">
         <v>79089</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490382</v>
+        <v>490192</v>
       </c>
       <c r="R2" t="n">
-        <v>6726363</v>
+        <v>6726244</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128561756</v>
+        <v>128560594</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490192</v>
+        <v>490358</v>
       </c>
       <c r="R3" t="n">
-        <v>6726244</v>
+        <v>6726368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128560594</v>
+        <v>128560143</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490358</v>
+        <v>490382</v>
       </c>
       <c r="R4" t="n">
-        <v>6726368</v>
+        <v>6726363</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562020</v>
+        <v>128562050</v>
       </c>
       <c r="B15" t="n">
         <v>79089</v>
@@ -2119,7 +2119,7 @@
         <v>490205</v>
       </c>
       <c r="R15" t="n">
-        <v>6726253</v>
+        <v>6726251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,6 +2162,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562050</v>
+        <v>128562020</v>
       </c>
       <c r="B16" t="n">
         <v>79089</v>
@@ -2226,7 +2231,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726251</v>
+        <v>6726253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,11 +2274,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560602</v>
+        <v>128560947</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490357</v>
+        <v>490328</v>
       </c>
       <c r="R21" t="n">
-        <v>6726365</v>
+        <v>6726400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2813,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560322</v>
+        <v>128560602</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2870,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490359</v>
+        <v>490357</v>
       </c>
       <c r="R22" t="n">
-        <v>6726325</v>
+        <v>6726365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560164</v>
+        <v>128560322</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490378</v>
+        <v>490359</v>
       </c>
       <c r="R23" t="n">
-        <v>6726352</v>
+        <v>6726325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560363</v>
+        <v>128560164</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -3084,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490366</v>
+        <v>490378</v>
       </c>
       <c r="R24" t="n">
-        <v>6726348</v>
+        <v>6726352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560947</v>
+        <v>128560363</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490328</v>
+        <v>490366</v>
       </c>
       <c r="R25" t="n">
-        <v>6726400</v>
+        <v>6726348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,12 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128561756</v>
+        <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490192</v>
+        <v>490382</v>
       </c>
       <c r="R2" t="n">
-        <v>6726244</v>
+        <v>6726363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128560594</v>
+        <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490358</v>
+        <v>490192</v>
       </c>
       <c r="R3" t="n">
-        <v>6726368</v>
+        <v>6726244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128560143</v>
+        <v>128560594</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490382</v>
+        <v>490358</v>
       </c>
       <c r="R4" t="n">
-        <v>6726363</v>
+        <v>6726368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128560947</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>128560602</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>128560322</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128560164</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128560363</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>128561664</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128560121</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128560783</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>128560602</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>128560322</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128560164</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128560363</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560947</v>
+        <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,39 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490328</v>
+        <v>490357</v>
       </c>
       <c r="R21" t="n">
-        <v>6726400</v>
+        <v>6726365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2813,12 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2835,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560602</v>
+        <v>128560322</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -2880,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490357</v>
+        <v>490359</v>
       </c>
       <c r="R22" t="n">
-        <v>6726365</v>
+        <v>6726325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,7 +2942,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560322</v>
+        <v>128560164</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -2987,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490359</v>
+        <v>490378</v>
       </c>
       <c r="R23" t="n">
-        <v>6726325</v>
+        <v>6726352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3049,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560164</v>
+        <v>128560363</v>
       </c>
       <c r="B24" t="n">
         <v>79120</v>
@@ -3094,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490378</v>
+        <v>490366</v>
       </c>
       <c r="R24" t="n">
-        <v>6726352</v>
+        <v>6726348</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560363</v>
+        <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,34 +3167,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490366</v>
+        <v>490328</v>
       </c>
       <c r="R25" t="n">
-        <v>6726348</v>
+        <v>6726400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3241,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560143</v>
+        <v>128560594</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490382</v>
+        <v>490358</v>
       </c>
       <c r="R2" t="n">
-        <v>6726363</v>
+        <v>6726368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128561756</v>
+        <v>128560143</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490192</v>
+        <v>490382</v>
       </c>
       <c r="R3" t="n">
-        <v>6726244</v>
+        <v>6726363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128560594</v>
+        <v>128561756</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490358</v>
+        <v>490192</v>
       </c>
       <c r="R4" t="n">
-        <v>6726368</v>
+        <v>6726244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128561671</v>
+        <v>128562020</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R14" t="n">
-        <v>6726241</v>
+        <v>6726253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562050</v>
+        <v>128561671</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R15" t="n">
-        <v>6726251</v>
+        <v>6726241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,12 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562020</v>
+        <v>128562050</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726253</v>
+        <v>6726251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2269,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128560322</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>128560363</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>128561664</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128560121</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128560783</v>
       </c>
       <c r="B31" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560594</v>
+        <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490358</v>
+        <v>490382</v>
       </c>
       <c r="R2" t="n">
-        <v>6726368</v>
+        <v>6726363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128560143</v>
+        <v>128561756</v>
       </c>
       <c r="B3" t="n">
         <v>79124</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490382</v>
+        <v>490192</v>
       </c>
       <c r="R3" t="n">
-        <v>6726363</v>
+        <v>6726244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128561756</v>
+        <v>128560594</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490192</v>
+        <v>490358</v>
       </c>
       <c r="R4" t="n">
-        <v>6726244</v>
+        <v>6726368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128562020</v>
+        <v>128561671</v>
       </c>
       <c r="B14" t="n">
         <v>79124</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R14" t="n">
-        <v>6726253</v>
+        <v>6726241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128561671</v>
+        <v>128562050</v>
       </c>
       <c r="B15" t="n">
         <v>79124</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R15" t="n">
-        <v>6726241</v>
+        <v>6726251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562050</v>
+        <v>128562020</v>
       </c>
       <c r="B16" t="n">
         <v>79124</v>
@@ -2226,7 +2231,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726251</v>
+        <v>6726253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,11 +2274,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128560322</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>128560363</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>128561664</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128560121</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128560783</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560143</v>
+        <v>128560594</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490382</v>
+        <v>490358</v>
       </c>
       <c r="R2" t="n">
-        <v>6726363</v>
+        <v>6726368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128561756</v>
+        <v>128560143</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490192</v>
+        <v>490382</v>
       </c>
       <c r="R3" t="n">
-        <v>6726244</v>
+        <v>6726363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128560594</v>
+        <v>128561756</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490358</v>
+        <v>490192</v>
       </c>
       <c r="R4" t="n">
-        <v>6726368</v>
+        <v>6726244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128560322</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>128560363</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560594</v>
+        <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490358</v>
+        <v>490382</v>
       </c>
       <c r="R2" t="n">
-        <v>6726368</v>
+        <v>6726363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128560143</v>
+        <v>128560594</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490382</v>
+        <v>490358</v>
       </c>
       <c r="R3" t="n">
-        <v>6726363</v>
+        <v>6726368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128560176</v>
+        <v>128561537</v>
       </c>
       <c r="B6" t="n">
         <v>79034</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490378</v>
+        <v>490229</v>
       </c>
       <c r="R6" t="n">
-        <v>6726345</v>
+        <v>6726211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128561306</v>
+        <v>128560176</v>
       </c>
       <c r="B7" t="n">
         <v>79034</v>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490251</v>
+        <v>490378</v>
       </c>
       <c r="R7" t="n">
-        <v>6726207</v>
+        <v>6726345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128561769</v>
+        <v>128561306</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1358,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490197</v>
+        <v>490251</v>
       </c>
       <c r="R8" t="n">
-        <v>6726291</v>
+        <v>6726207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128561537</v>
+        <v>128561769</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1465,14 +1470,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490229</v>
+        <v>490197</v>
       </c>
       <c r="R9" t="n">
-        <v>6726211</v>
+        <v>6726291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128560102</v>
+        <v>128561932</v>
       </c>
       <c r="B11" t="n">
         <v>79034</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490383</v>
+        <v>490206</v>
       </c>
       <c r="R11" t="n">
-        <v>6726365</v>
+        <v>6726252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128561932</v>
+        <v>128560102</v>
       </c>
       <c r="B12" t="n">
         <v>79034</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490206</v>
+        <v>490383</v>
       </c>
       <c r="R12" t="n">
-        <v>6726252</v>
+        <v>6726365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128561671</v>
+        <v>128562020</v>
       </c>
       <c r="B14" t="n">
         <v>79034</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R14" t="n">
-        <v>6726241</v>
+        <v>6726253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562050</v>
+        <v>128561671</v>
       </c>
       <c r="B15" t="n">
         <v>79034</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R15" t="n">
-        <v>6726251</v>
+        <v>6726241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,12 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562020</v>
+        <v>128562050</v>
       </c>
       <c r="B16" t="n">
         <v>79034</v>
@@ -2231,7 +2226,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726253</v>
+        <v>6726251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2269,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128561297</v>
+        <v>128560679</v>
       </c>
       <c r="B19" t="n">
         <v>79034</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490248</v>
+        <v>490342</v>
       </c>
       <c r="R19" t="n">
-        <v>6726196</v>
+        <v>6726362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128560679</v>
+        <v>128561297</v>
       </c>
       <c r="B20" t="n">
         <v>79034</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490342</v>
+        <v>490248</v>
       </c>
       <c r="R20" t="n">
-        <v>6726362</v>
+        <v>6726196</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560322</v>
+        <v>128560947</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,34 +2846,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490359</v>
+        <v>490328</v>
       </c>
       <c r="R22" t="n">
-        <v>6726325</v>
+        <v>6726400</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2910,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2920,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560164</v>
+        <v>128560322</v>
       </c>
       <c r="B23" t="n">
         <v>79034</v>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490378</v>
+        <v>490359</v>
       </c>
       <c r="R23" t="n">
-        <v>6726352</v>
+        <v>6726325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560947</v>
+        <v>128560164</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490328</v>
+        <v>490378</v>
       </c>
       <c r="R25" t="n">
-        <v>6726400</v>
+        <v>6726352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,12 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128560143</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128560594</v>
+        <v>128561756</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490358</v>
+        <v>490192</v>
       </c>
       <c r="R3" t="n">
-        <v>6726368</v>
+        <v>6726244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128561756</v>
+        <v>128560594</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490192</v>
+        <v>490358</v>
       </c>
       <c r="R4" t="n">
-        <v>6726244</v>
+        <v>6726368</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>128561256</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128561537</v>
+        <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490229</v>
+        <v>490378</v>
       </c>
       <c r="R6" t="n">
-        <v>6726211</v>
+        <v>6726345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128560176</v>
+        <v>128561306</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490378</v>
+        <v>490251</v>
       </c>
       <c r="R7" t="n">
-        <v>6726345</v>
+        <v>6726207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128561306</v>
+        <v>128561769</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490251</v>
+        <v>490197</v>
       </c>
       <c r="R8" t="n">
-        <v>6726207</v>
+        <v>6726291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128561769</v>
+        <v>128561537</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,14 +1465,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490197</v>
+        <v>490229</v>
       </c>
       <c r="R9" t="n">
-        <v>6726291</v>
+        <v>6726211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
         <v>128560234</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128561932</v>
+        <v>128560102</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490206</v>
+        <v>490383</v>
       </c>
       <c r="R11" t="n">
-        <v>6726252</v>
+        <v>6726365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128560102</v>
+        <v>128561932</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490383</v>
+        <v>490206</v>
       </c>
       <c r="R12" t="n">
-        <v>6726365</v>
+        <v>6726252</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
         <v>128561685</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128562020</v>
+        <v>128561671</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490205</v>
+        <v>490192</v>
       </c>
       <c r="R14" t="n">
-        <v>6726253</v>
+        <v>6726241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128561671</v>
+        <v>128562050</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490192</v>
+        <v>490205</v>
       </c>
       <c r="R15" t="n">
-        <v>6726241</v>
+        <v>6726251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562050</v>
+        <v>128562020</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2231,7 @@
         <v>490205</v>
       </c>
       <c r="R16" t="n">
-        <v>6726251</v>
+        <v>6726253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,11 +2274,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,7 +2303,7 @@
         <v>128560202</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>128560696</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128560679</v>
+        <v>128561297</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490342</v>
+        <v>490248</v>
       </c>
       <c r="R19" t="n">
-        <v>6726362</v>
+        <v>6726196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128561297</v>
+        <v>128560679</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490248</v>
+        <v>490342</v>
       </c>
       <c r="R20" t="n">
-        <v>6726196</v>
+        <v>6726362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,7 +2731,7 @@
         <v>128560602</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560947</v>
+        <v>128560322</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,39 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490328</v>
+        <v>490359</v>
       </c>
       <c r="R22" t="n">
-        <v>6726400</v>
+        <v>6726325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2920,12 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560322</v>
+        <v>128560164</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2987,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490359</v>
+        <v>490378</v>
       </c>
       <c r="R23" t="n">
-        <v>6726325</v>
+        <v>6726352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,7 +3052,7 @@
         <v>128560363</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560164</v>
+        <v>128560947</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,34 +3167,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490378</v>
+        <v>490328</v>
       </c>
       <c r="R25" t="n">
-        <v>6726352</v>
+        <v>6726400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3241,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3276,7 +3276,7 @@
         <v>128560652</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128560299</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128561642</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560602</v>
+        <v>128560947</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490357</v>
+        <v>490328</v>
       </c>
       <c r="R21" t="n">
-        <v>6726365</v>
+        <v>6726400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2813,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560322</v>
+        <v>128560602</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2870,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490359</v>
+        <v>490357</v>
       </c>
       <c r="R22" t="n">
-        <v>6726325</v>
+        <v>6726365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560164</v>
+        <v>128560322</v>
       </c>
       <c r="B23" t="n">
         <v>79035</v>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490378</v>
+        <v>490359</v>
       </c>
       <c r="R23" t="n">
-        <v>6726352</v>
+        <v>6726325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560363</v>
+        <v>128560164</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -3084,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490366</v>
+        <v>490378</v>
       </c>
       <c r="R24" t="n">
-        <v>6726348</v>
+        <v>6726352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560947</v>
+        <v>128560363</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,39 +3177,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490328</v>
+        <v>490366</v>
       </c>
       <c r="R25" t="n">
-        <v>6726400</v>
+        <v>6726348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,12 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128560143</v>
+        <v>128560068</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490382</v>
+        <v>490384</v>
       </c>
       <c r="R2" t="n">
-        <v>6726363</v>
+        <v>6726393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128561756</v>
+        <v>128560102</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490192</v>
+        <v>490383</v>
       </c>
       <c r="R3" t="n">
-        <v>6726244</v>
+        <v>6726365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten fläck med naturskogskaraktär.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128560594</v>
+        <v>128560143</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490358</v>
+        <v>490382</v>
       </c>
       <c r="R4" t="n">
-        <v>6726368</v>
+        <v>6726363</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128561256</v>
+        <v>128560164</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490249</v>
+        <v>490378</v>
       </c>
       <c r="R5" t="n">
-        <v>6726244</v>
+        <v>6726352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,11 +1106,11 @@
         <v>128560176</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1220,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128561306</v>
+        <v>128560187</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490251</v>
+        <v>490377</v>
       </c>
       <c r="R7" t="n">
-        <v>6726207</v>
+        <v>6726345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128561769</v>
+        <v>128560227</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1358,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490197</v>
+        <v>490371</v>
       </c>
       <c r="R8" t="n">
-        <v>6726291</v>
+        <v>6726332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128561537</v>
+        <v>128560299</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490229</v>
+        <v>490370</v>
       </c>
       <c r="R9" t="n">
-        <v>6726211</v>
+        <v>6726320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128560234</v>
+        <v>128560322</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1581,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490371</v>
+        <v>490359</v>
       </c>
       <c r="R10" t="n">
-        <v>6726332</v>
+        <v>6726325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128560102</v>
+        <v>128560363</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1688,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490383</v>
+        <v>490366</v>
       </c>
       <c r="R11" t="n">
-        <v>6726365</v>
+        <v>6726348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128561932</v>
+        <v>128560602</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1795,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490206</v>
+        <v>490357</v>
       </c>
       <c r="R12" t="n">
-        <v>6726252</v>
+        <v>6726365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128561685</v>
+        <v>128560652</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1902,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490192</v>
+        <v>490343</v>
       </c>
       <c r="R13" t="n">
-        <v>6726243</v>
+        <v>6726362</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128561671</v>
+        <v>128560679</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2009,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490192</v>
+        <v>490342</v>
       </c>
       <c r="R14" t="n">
-        <v>6726241</v>
+        <v>6726362</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128562050</v>
+        <v>128560694</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2116,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490205</v>
+        <v>490342</v>
       </c>
       <c r="R15" t="n">
-        <v>6726251</v>
+        <v>6726361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,12 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav på tall och gran.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128562020</v>
+        <v>128561247</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2228,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490205</v>
+        <v>490249</v>
       </c>
       <c r="R16" t="n">
-        <v>6726253</v>
+        <v>6726244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,14 +2280,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128560202</v>
+        <v>128561296</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2335,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490377</v>
+        <v>490248</v>
       </c>
       <c r="R17" t="n">
-        <v>6726345</v>
+        <v>6726196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,14 +2387,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128560696</v>
+        <v>128561306</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2442,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490342</v>
+        <v>490251</v>
       </c>
       <c r="R18" t="n">
-        <v>6726361</v>
+        <v>6726207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,14 +2494,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128561297</v>
+        <v>128561537</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2549,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490248</v>
+        <v>490229</v>
       </c>
       <c r="R19" t="n">
-        <v>6726196</v>
+        <v>6726211</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2574,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,14 +2606,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128560679</v>
+        <v>128561642</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2652,14 +2637,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490342</v>
+        <v>490185</v>
       </c>
       <c r="R20" t="n">
-        <v>6726362</v>
+        <v>6726235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,50 +2713,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128560947</v>
+        <v>128561671</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490328</v>
+        <v>490192</v>
       </c>
       <c r="R21" t="n">
-        <v>6726400</v>
+        <v>6726241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2813,12 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,14 +2820,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128560602</v>
+        <v>128561683</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2880,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490357</v>
+        <v>490192</v>
       </c>
       <c r="R22" t="n">
-        <v>6726365</v>
+        <v>6726243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,14 +2927,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128560322</v>
+        <v>128561731</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2987,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490359</v>
+        <v>490192</v>
       </c>
       <c r="R23" t="n">
-        <v>6726325</v>
+        <v>6726244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3007,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Liten fläck med naturskogskaraktär.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,14 +3039,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128560164</v>
+        <v>128561767</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3090,14 +3070,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörkån, Mörkån, Dlr</t>
+          <t>Sundslidberget, Sundslidberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490378</v>
+        <v>490197</v>
       </c>
       <c r="R24" t="n">
-        <v>6726352</v>
+        <v>6726291</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,14 +3146,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128560363</v>
+        <v>128561921</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3201,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490366</v>
+        <v>490206</v>
       </c>
       <c r="R25" t="n">
-        <v>6726348</v>
+        <v>6726252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3246,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,14 +3253,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128560652</v>
+        <v>128562020</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3308,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490343</v>
+        <v>490205</v>
       </c>
       <c r="R26" t="n">
-        <v>6726362</v>
+        <v>6726253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3343,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3353,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3380,50 +3360,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128561664</v>
+        <v>128562050</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490190</v>
+        <v>490205</v>
       </c>
       <c r="R27" t="n">
-        <v>6726240</v>
+        <v>6726251</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3455,7 +3430,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3465,12 +3440,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt med Garnlav på tall och gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128560299</v>
+        <v>128560121</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,34 +3483,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490370</v>
+        <v>490382</v>
       </c>
       <c r="R28" t="n">
-        <v>6726320</v>
+        <v>6726363</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3577,7 +3557,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128561642</v>
+        <v>128560783</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,34 +3600,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundslidberget, Sundslidberget, Dlr</t>
+          <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490185</v>
+        <v>490346</v>
       </c>
       <c r="R29" t="n">
-        <v>6726235</v>
+        <v>6726349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3664,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3674,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128560121</v>
+        <v>128560947</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490382</v>
+        <v>490328</v>
       </c>
       <c r="R30" t="n">
-        <v>6726363</v>
+        <v>6726400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3781,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3796,7 +3791,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3828,10 +3823,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128560783</v>
+        <v>128561664</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3868,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490346</v>
+        <v>490190</v>
       </c>
       <c r="R31" t="n">
-        <v>6726349</v>
+        <v>6726240</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,7 +3898,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3913,12 +3908,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,6 +3937,118 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128560594</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490358</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6726368</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41528-2025 artfynd.xlsx
+++ b/artfynd/A 41528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560102</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560143</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560164</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560187</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560322</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560363</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560602</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560652</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560679</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560694</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561247</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561296</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561306</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561537</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561642</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561671</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561683</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561731</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3143,6 +3258,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561767</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3250,6 +3370,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561921</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128562020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3469,6 +3599,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128562050</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3586,6 +3721,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560121</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3703,6 +3843,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560783</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3820,6 +3965,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560947</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3937,6 +4087,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128561664</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4049,8 +4204,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128560594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>